--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/79.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/79.xlsx
@@ -426,13 +426,13 @@
         <v>-9.552627721682473</v>
       </c>
       <c r="E2">
-        <v>-19.92805460807586</v>
+        <v>-18.63363559772337</v>
       </c>
       <c r="F2">
-        <v>-1.951745577842521</v>
+        <v>-1.406306233101784</v>
       </c>
       <c r="G2">
-        <v>-18.51994935700708</v>
+        <v>-16.19230975416382</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.607596075672092</v>
       </c>
       <c r="E3">
-        <v>-21.85295946909428</v>
+        <v>-19.58623180455488</v>
       </c>
       <c r="F3">
-        <v>-1.800571840301222</v>
+        <v>-1.141995732420934</v>
       </c>
       <c r="G3">
-        <v>-17.86627882973244</v>
+        <v>-15.54441612885521</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.577627824886119</v>
       </c>
       <c r="E4">
-        <v>-21.53482964158143</v>
+        <v>-20.8778295756006</v>
       </c>
       <c r="F4">
-        <v>-1.505340869576076</v>
+        <v>-1.267479311699212</v>
       </c>
       <c r="G4">
-        <v>-17.71623828480159</v>
+        <v>-16.27296457513708</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.557891087138806</v>
       </c>
       <c r="E5">
-        <v>-21.38919391749475</v>
+        <v>-20.7899228381637</v>
       </c>
       <c r="F5">
-        <v>-1.608296168967818</v>
+        <v>-1.090520982010973</v>
       </c>
       <c r="G5">
-        <v>-17.04897962336102</v>
+        <v>-15.96016105876796</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.541033051014471</v>
       </c>
       <c r="E6">
-        <v>-21.54196651661751</v>
+        <v>-22.04094548210069</v>
       </c>
       <c r="F6">
-        <v>-1.898210677701797</v>
+        <v>-1.30550468895732</v>
       </c>
       <c r="G6">
-        <v>-16.6388857946838</v>
+        <v>-15.60712779300562</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.554525928770686</v>
       </c>
       <c r="E7">
-        <v>-23.29523315579721</v>
+        <v>-23.01861584951267</v>
       </c>
       <c r="F7">
-        <v>-1.401022077439326</v>
+        <v>-0.8955481464140532</v>
       </c>
       <c r="G7">
-        <v>-15.79071244061314</v>
+        <v>-14.94410166403701</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.599493303631871</v>
       </c>
       <c r="E8">
-        <v>-23.36464107691277</v>
+        <v>-23.66722465315729</v>
       </c>
       <c r="F8">
-        <v>-1.112509166350883</v>
+        <v>-0.8557972798559134</v>
       </c>
       <c r="G8">
-        <v>-15.38103739594664</v>
+        <v>-14.36448307465756</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.705041322260187</v>
       </c>
       <c r="E9">
-        <v>-23.99022711870239</v>
+        <v>-23.90271888697817</v>
       </c>
       <c r="F9">
-        <v>-1.782132381914905</v>
+        <v>-0.7079254147821736</v>
       </c>
       <c r="G9">
-        <v>-15.22584233161114</v>
+        <v>-14.3473361040369</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.878359557020691</v>
       </c>
       <c r="E10">
-        <v>-25.25416044203525</v>
+        <v>-23.78212562415391</v>
       </c>
       <c r="F10">
-        <v>-1.094089588782233</v>
+        <v>-0.6607440926209222</v>
       </c>
       <c r="G10">
-        <v>-14.9343769365154</v>
+        <v>-13.08172116546461</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.142894930169296</v>
       </c>
       <c r="E11">
-        <v>-25.90734300442762</v>
+        <v>-24.87674383281398</v>
       </c>
       <c r="F11">
-        <v>-0.8972289038743335</v>
+        <v>-0.7170440831521906</v>
       </c>
       <c r="G11">
-        <v>-13.97720221529146</v>
+        <v>-13.62033368252187</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.514705033788598</v>
       </c>
       <c r="E12">
-        <v>-27.21727656673039</v>
+        <v>-26.03368742924162</v>
       </c>
       <c r="F12">
-        <v>-0.4739580120658701</v>
+        <v>-0.4495675622578414</v>
       </c>
       <c r="G12">
-        <v>-13.40628373958921</v>
+        <v>-13.18484134846737</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.001350219983120472</v>
       </c>
       <c r="E13">
-        <v>-26.65290190810245</v>
+        <v>-27.6639109011589</v>
       </c>
       <c r="F13">
-        <v>-0.603377164874848</v>
+        <v>-0.1963820357965894</v>
       </c>
       <c r="G13">
-        <v>-13.09417874832888</v>
+        <v>-11.75595030389822</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.384832373604758</v>
       </c>
       <c r="E14">
-        <v>-28.08529446452064</v>
+        <v>-27.37412479246006</v>
       </c>
       <c r="F14">
-        <v>-0.09730846605436567</v>
+        <v>0.07116158285738658</v>
       </c>
       <c r="G14">
-        <v>-13.49178188868643</v>
+        <v>-10.92695990595486</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.6550365285421323</v>
       </c>
       <c r="E15">
-        <v>-30.05696034814227</v>
+        <v>-27.10306392378294</v>
       </c>
       <c r="F15">
-        <v>-0.02868568203905183</v>
+        <v>0.1297163894590752</v>
       </c>
       <c r="G15">
-        <v>-12.42480630356149</v>
+        <v>-11.17493631957396</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.8234728896475246</v>
       </c>
       <c r="E16">
-        <v>-29.04341540964151</v>
+        <v>-29.11345278864415</v>
       </c>
       <c r="F16">
-        <v>-0.1561730820647013</v>
+        <v>0.3095806319963347</v>
       </c>
       <c r="G16">
-        <v>-12.2855614476342</v>
+        <v>-10.27754674024372</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.9149263057331055</v>
       </c>
       <c r="E17">
-        <v>-31.37626332316691</v>
+        <v>-29.42841494858863</v>
       </c>
       <c r="F17">
-        <v>0.3514463205338217</v>
+        <v>0.5097291071259457</v>
       </c>
       <c r="G17">
-        <v>-10.72472198950632</v>
+        <v>-10.61121993569241</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.9602192213143418</v>
       </c>
       <c r="E18">
-        <v>-30.83784587755093</v>
+        <v>-31.53344892021015</v>
       </c>
       <c r="F18">
-        <v>0.3485594601350654</v>
+        <v>1.040832725593835</v>
       </c>
       <c r="G18">
-        <v>-11.11146322994952</v>
+        <v>-9.864192024210324</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.9848758860902374</v>
       </c>
       <c r="E19">
-        <v>-32.29096073102823</v>
+        <v>-31.86942093531322</v>
       </c>
       <c r="F19">
-        <v>0.9814636338351941</v>
+        <v>1.048337734263198</v>
       </c>
       <c r="G19">
-        <v>-9.906163120557203</v>
+        <v>-9.510499959885667</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.017240924994678</v>
       </c>
       <c r="E20">
-        <v>-32.61572024448831</v>
+        <v>-31.81816540225741</v>
       </c>
       <c r="F20">
-        <v>0.8136430249672366</v>
+        <v>1.124479609193723</v>
       </c>
       <c r="G20">
-        <v>-10.78316967100215</v>
+        <v>-8.706464454217336</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.075375340862322</v>
       </c>
       <c r="E21">
-        <v>-33.87621419181234</v>
+        <v>-32.77747507180529</v>
       </c>
       <c r="F21">
-        <v>1.036334690596633</v>
+        <v>1.300007348377327</v>
       </c>
       <c r="G21">
-        <v>-9.984662776384402</v>
+        <v>-8.722421283716622</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.174561387395485</v>
       </c>
       <c r="E22">
-        <v>-33.7743484332468</v>
+        <v>-33.60586202931741</v>
       </c>
       <c r="F22">
-        <v>1.16295727505376</v>
+        <v>1.689142876251229</v>
       </c>
       <c r="G22">
-        <v>-10.1544838309124</v>
+        <v>-8.78734439228727</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.320115817267335</v>
       </c>
       <c r="E23">
-        <v>-34.56368862362779</v>
+        <v>-34.48243421450816</v>
       </c>
       <c r="F23">
-        <v>1.188321884927481</v>
+        <v>1.816464602796318</v>
       </c>
       <c r="G23">
-        <v>-9.457524610166251</v>
+        <v>-8.494367733152849</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.511823923396338</v>
       </c>
       <c r="E24">
-        <v>-33.98622893935468</v>
+        <v>-34.14830981680022</v>
       </c>
       <c r="F24">
-        <v>1.441280438720366</v>
+        <v>1.87485456428485</v>
       </c>
       <c r="G24">
-        <v>-9.890980958714106</v>
+        <v>-8.594240270981581</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.744999113242383</v>
       </c>
       <c r="E25">
-        <v>-34.08079932629387</v>
+        <v>-34.88363663345472</v>
       </c>
       <c r="F25">
-        <v>1.308484860377577</v>
+        <v>1.692239313602893</v>
       </c>
       <c r="G25">
-        <v>-9.554477246829347</v>
+        <v>-7.783497600050686</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.007002348664871</v>
       </c>
       <c r="E26">
-        <v>-34.81263695372546</v>
+        <v>-34.75839036358757</v>
       </c>
       <c r="F26">
-        <v>1.091401242065133</v>
+        <v>1.510442489914902</v>
       </c>
       <c r="G26">
-        <v>-10.33108819325036</v>
+        <v>-8.550647007320459</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.28555353889683</v>
       </c>
       <c r="E27">
-        <v>-34.49234704411095</v>
+        <v>-34.89379626489093</v>
       </c>
       <c r="F27">
-        <v>1.010072130458278</v>
+        <v>1.599641091848353</v>
       </c>
       <c r="G27">
-        <v>-9.953692622864519</v>
+        <v>-8.644908170460127</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.561381850322792</v>
       </c>
       <c r="E28">
-        <v>-34.52261083590421</v>
+        <v>-34.10057290804836</v>
       </c>
       <c r="F28">
-        <v>1.515003480834716</v>
+        <v>2.093232092480466</v>
       </c>
       <c r="G28">
-        <v>-8.771662338067742</v>
+        <v>-7.970801645571571</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.815984061411156</v>
       </c>
       <c r="E29">
-        <v>-35.01503709949829</v>
+        <v>-34.38076997303596</v>
       </c>
       <c r="F29">
-        <v>1.276705373336577</v>
+        <v>1.715054208610797</v>
       </c>
       <c r="G29">
-        <v>-10.12802595096254</v>
+        <v>-8.117409154778196</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.03076139443808</v>
       </c>
       <c r="E30">
-        <v>-33.57723528087793</v>
+        <v>-34.51453430251153</v>
       </c>
       <c r="F30">
-        <v>0.8038003634871729</v>
+        <v>1.705029306302117</v>
       </c>
       <c r="G30">
-        <v>-10.00693943731816</v>
+        <v>-8.576396430524911</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.187237585423169</v>
       </c>
       <c r="E31">
-        <v>-34.12132916866252</v>
+        <v>-33.89510472113534</v>
       </c>
       <c r="F31">
-        <v>0.7471367196660755</v>
+        <v>1.596524773679021</v>
       </c>
       <c r="G31">
-        <v>-10.24764920347856</v>
+        <v>-8.914452788267587</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.272321529377936</v>
       </c>
       <c r="E32">
-        <v>-33.80538206562137</v>
+        <v>-33.3173891780808</v>
       </c>
       <c r="F32">
-        <v>0.4904670799086487</v>
+        <v>1.588704985396594</v>
       </c>
       <c r="G32">
-        <v>-10.05327714323134</v>
+        <v>-9.109652484899634</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.275463164962253</v>
       </c>
       <c r="E33">
-        <v>-33.66839346265233</v>
+        <v>-33.40276223431041</v>
       </c>
       <c r="F33">
-        <v>0.7367440222305529</v>
+        <v>1.518736104351731</v>
       </c>
       <c r="G33">
-        <v>-9.44008465626537</v>
+        <v>-8.679341154614086</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.193680518659885</v>
       </c>
       <c r="E34">
-        <v>-32.20179960629121</v>
+        <v>-33.93672592573984</v>
       </c>
       <c r="F34">
-        <v>0.7406456326977386</v>
+        <v>1.573481249267945</v>
       </c>
       <c r="G34">
-        <v>-10.38995962457522</v>
+        <v>-8.850281173534354</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.027979060580818</v>
       </c>
       <c r="E35">
-        <v>-31.43332662413756</v>
+        <v>-31.76799670296343</v>
       </c>
       <c r="F35">
-        <v>0.7829718935111821</v>
+        <v>1.646632717874364</v>
       </c>
       <c r="G35">
-        <v>-10.53115439182513</v>
+        <v>-8.830921103220696</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.785501512262234</v>
       </c>
       <c r="E36">
-        <v>-30.91489786279145</v>
+        <v>-32.12221620408041</v>
       </c>
       <c r="F36">
-        <v>0.7264043403088095</v>
+        <v>1.630532569033552</v>
       </c>
       <c r="G36">
-        <v>-10.78437139903291</v>
+        <v>-9.057097574463704</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.476709435372035</v>
       </c>
       <c r="E37">
-        <v>-31.09437940161145</v>
+        <v>-30.4046022407631</v>
       </c>
       <c r="F37">
-        <v>1.078303096692067</v>
+        <v>1.577039915630371</v>
       </c>
       <c r="G37">
-        <v>-10.46817457348604</v>
+        <v>-10.22526991563309</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.112377853470035</v>
       </c>
       <c r="E38">
-        <v>-30.44526114464097</v>
+        <v>-30.4848966133931</v>
       </c>
       <c r="F38">
-        <v>1.052383480658471</v>
+        <v>1.412802824146925</v>
       </c>
       <c r="G38">
-        <v>-10.73601094979523</v>
+        <v>-9.12738376680797</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.706656409183511</v>
       </c>
       <c r="E39">
-        <v>-30.12020501613339</v>
+        <v>-29.79357977138215</v>
       </c>
       <c r="F39">
-        <v>0.6056714480855871</v>
+        <v>1.448089618771378</v>
       </c>
       <c r="G39">
-        <v>-10.11862069108547</v>
+        <v>-9.171460370117828</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.269669497743326</v>
       </c>
       <c r="E40">
-        <v>-29.5518453003787</v>
+        <v>-29.5471809721508</v>
       </c>
       <c r="F40">
-        <v>0.6537780566357657</v>
+        <v>1.168402962359764</v>
       </c>
       <c r="G40">
-        <v>-11.6757291643906</v>
+        <v>-9.818324415763721</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.8143893937276916</v>
       </c>
       <c r="E41">
-        <v>-28.95743327365788</v>
+        <v>-29.929873253591</v>
       </c>
       <c r="F41">
-        <v>0.8903697272841381</v>
+        <v>1.525546941137549</v>
       </c>
       <c r="G41">
-        <v>-11.23428446945648</v>
+        <v>-9.34901154848002</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.3505133292999518</v>
       </c>
       <c r="E42">
-        <v>-28.96756799848704</v>
+        <v>-27.8371295604263</v>
       </c>
       <c r="F42">
-        <v>1.056063088661706</v>
+        <v>1.402955192462444</v>
       </c>
       <c r="G42">
-        <v>-11.14423100969722</v>
+        <v>-10.30016438736802</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.1151228291469721</v>
       </c>
       <c r="E43">
-        <v>-27.90897380055799</v>
+        <v>-28.18630207726173</v>
       </c>
       <c r="F43">
-        <v>0.8541419072901045</v>
+        <v>1.545694493108438</v>
       </c>
       <c r="G43">
-        <v>-12.79274033479609</v>
+        <v>-9.192968984486471</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.5721902132627402</v>
       </c>
       <c r="E44">
-        <v>-27.33168846253418</v>
+        <v>-28.14720776115351</v>
       </c>
       <c r="F44">
-        <v>0.7905945303517432</v>
+        <v>1.862440650386496</v>
       </c>
       <c r="G44">
-        <v>-11.85741852467688</v>
+        <v>-9.996349002138029</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.016728123471813</v>
       </c>
       <c r="E45">
-        <v>-26.79180831981373</v>
+        <v>-27.54410559281198</v>
       </c>
       <c r="F45">
-        <v>0.9569406452427175</v>
+        <v>1.482637509672534</v>
       </c>
       <c r="G45">
-        <v>-11.54581673633852</v>
+        <v>-10.35341120182166</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.440132633711373</v>
       </c>
       <c r="E46">
-        <v>-25.93902420858528</v>
+        <v>-27.2572494067961</v>
       </c>
       <c r="F46">
-        <v>1.308521308543301</v>
+        <v>1.707426601565819</v>
       </c>
       <c r="G46">
-        <v>-12.08701147891641</v>
+        <v>-10.45748482193973</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.83827783643203</v>
       </c>
       <c r="E47">
-        <v>-25.91174468116307</v>
+        <v>-26.57345888858589</v>
       </c>
       <c r="F47">
-        <v>0.7833562559860812</v>
+        <v>1.77258929493964</v>
       </c>
       <c r="G47">
-        <v>-12.74924969804668</v>
+        <v>-11.26329478001711</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.209017073187301</v>
       </c>
       <c r="E48">
-        <v>-25.48847727261414</v>
+        <v>-25.73022532903962</v>
       </c>
       <c r="F48">
-        <v>0.6636521960771358</v>
+        <v>1.604614609734761</v>
       </c>
       <c r="G48">
-        <v>-11.98620205670007</v>
+        <v>-10.42419066545128</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.548046988403595</v>
       </c>
       <c r="E49">
-        <v>-25.28343702649484</v>
+        <v>-25.46776403250306</v>
       </c>
       <c r="F49">
-        <v>1.181325493843436</v>
+        <v>1.424346952272339</v>
       </c>
       <c r="G49">
-        <v>-12.0650592514455</v>
+        <v>-10.74150645539042</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.858673007477901</v>
       </c>
       <c r="E50">
-        <v>-24.30566703265469</v>
+        <v>-25.01032023061823</v>
       </c>
       <c r="F50">
-        <v>1.034311817398997</v>
+        <v>1.381855017978335</v>
       </c>
       <c r="G50">
-        <v>-12.56790132395095</v>
+        <v>-10.38795343397842</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.139024538959394</v>
       </c>
       <c r="E51">
-        <v>-24.65976652921047</v>
+        <v>-23.24199641536304</v>
       </c>
       <c r="F51">
-        <v>0.6449029282821718</v>
+        <v>1.571784752827011</v>
       </c>
       <c r="G51">
-        <v>-13.23169881003021</v>
+        <v>-10.4894911762134</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.393521851764787</v>
       </c>
       <c r="E52">
-        <v>-23.65613894878651</v>
+        <v>-23.51459696520277</v>
       </c>
       <c r="F52">
-        <v>0.8784776848495484</v>
+        <v>1.600984703775694</v>
       </c>
       <c r="G52">
-        <v>-12.67744065475435</v>
+        <v>-10.53168738965696</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.625868041665798</v>
       </c>
       <c r="E53">
-        <v>-23.04253072074718</v>
+        <v>-22.70456617708074</v>
       </c>
       <c r="F53">
-        <v>1.09122562817574</v>
+        <v>1.538239186483243</v>
       </c>
       <c r="G53">
-        <v>-12.71570062955171</v>
+        <v>-10.98026299968266</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.837904237388028</v>
       </c>
       <c r="E54">
-        <v>-22.6571394687984</v>
+        <v>-23.25341269833637</v>
       </c>
       <c r="F54">
-        <v>0.6300030838080171</v>
+        <v>1.881673684744695</v>
       </c>
       <c r="G54">
-        <v>-11.7477467720519</v>
+        <v>-11.09400010222986</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.037418445793035</v>
       </c>
       <c r="E55">
-        <v>-22.85146081694154</v>
+        <v>-21.43034416080245</v>
       </c>
       <c r="F55">
-        <v>0.5800889775849301</v>
+        <v>0.9346111735328541</v>
       </c>
       <c r="G55">
-        <v>-13.1164520987171</v>
+        <v>-10.59148908427835</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.223728422720656</v>
       </c>
       <c r="E56">
-        <v>-22.10451167174636</v>
+        <v>-22.08881145236176</v>
       </c>
       <c r="F56">
-        <v>0.3686755341446486</v>
+        <v>1.026301504613926</v>
       </c>
       <c r="G56">
-        <v>-12.47452076592472</v>
+        <v>-10.66430122286908</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.402031429671482</v>
       </c>
       <c r="E57">
-        <v>-21.49212613168909</v>
+        <v>-20.8587013013922</v>
       </c>
       <c r="F57">
-        <v>0.5330244552274733</v>
+        <v>1.393897823280234</v>
       </c>
       <c r="G57">
-        <v>-12.92738684296932</v>
+        <v>-11.29836338891461</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.571442105024784</v>
       </c>
       <c r="E58">
-        <v>-21.15359552877169</v>
+        <v>-20.45356137429597</v>
       </c>
       <c r="F58">
-        <v>0.3641592750645857</v>
+        <v>1.018899213502509</v>
       </c>
       <c r="G58">
-        <v>-12.92673797604363</v>
+        <v>-11.08372085833042</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.728101691980991</v>
       </c>
       <c r="E59">
-        <v>-21.17363402625563</v>
+        <v>-20.14379563827529</v>
       </c>
       <c r="F59">
-        <v>0.3545618103357506</v>
+        <v>0.6964886799241081</v>
       </c>
       <c r="G59">
-        <v>-12.94505853505795</v>
+        <v>-11.06197057413741</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.872630318259434</v>
       </c>
       <c r="E60">
-        <v>-20.2663723727149</v>
+        <v>-20.16939510184065</v>
       </c>
       <c r="F60">
-        <v>0.6447753597021406</v>
+        <v>1.052454720255112</v>
       </c>
       <c r="G60">
-        <v>-12.44380221386582</v>
+        <v>-11.38277567907495</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.996120656403126</v>
       </c>
       <c r="E61">
-        <v>-20.96182371149487</v>
+        <v>-19.94180305516315</v>
       </c>
       <c r="F61">
-        <v>0.2295694529273332</v>
+        <v>0.9848748507999224</v>
       </c>
       <c r="G61">
-        <v>-11.9408773777219</v>
+        <v>-10.73777547056766</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.098670349227049</v>
       </c>
       <c r="E62">
-        <v>-20.38481913885953</v>
+        <v>-19.40397883964218</v>
       </c>
       <c r="F62">
-        <v>0.3440075812566821</v>
+        <v>1.025945306630722</v>
       </c>
       <c r="G62">
-        <v>-12.52718492436345</v>
+        <v>-11.58630801882934</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.175213655837802</v>
       </c>
       <c r="E63">
-        <v>-19.22196588385188</v>
+        <v>-19.54597367062669</v>
       </c>
       <c r="F63">
-        <v>0.4441124684153912</v>
+        <v>1.060963710216668</v>
       </c>
       <c r="G63">
-        <v>-12.57127145930992</v>
+        <v>-12.12610902173521</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.221362291455854</v>
       </c>
       <c r="E64">
-        <v>-19.00430930914722</v>
+        <v>-18.39770210192374</v>
       </c>
       <c r="F64">
-        <v>0.5964202409311223</v>
+        <v>0.51987080923842</v>
       </c>
       <c r="G64">
-        <v>-12.58260014614531</v>
+        <v>-11.68793845633943</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.239685693658402</v>
       </c>
       <c r="E65">
-        <v>-19.60477137714228</v>
+        <v>-19.06725056937983</v>
       </c>
       <c r="F65">
-        <v>0.07015511646298518</v>
+        <v>0.9893877964103741</v>
       </c>
       <c r="G65">
-        <v>-13.58791682060133</v>
+        <v>-11.11657802280769</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.224999008773776</v>
       </c>
       <c r="E66">
-        <v>-19.32868843079065</v>
+        <v>-18.72497491845808</v>
       </c>
       <c r="F66">
-        <v>0.06596357740481967</v>
+        <v>0.601974444366893</v>
       </c>
       <c r="G66">
-        <v>-13.37759124140035</v>
+        <v>-11.62199238919715</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.183674311358121</v>
       </c>
       <c r="E67">
-        <v>-19.63210524625258</v>
+        <v>-19.57912662883685</v>
       </c>
       <c r="F67">
-        <v>0.3293446498597281</v>
+        <v>0.741689375625266</v>
       </c>
       <c r="G67">
-        <v>-13.18749640598986</v>
+        <v>-12.84657642635571</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.117482341563749</v>
       </c>
       <c r="E68">
-        <v>-18.78333789146893</v>
+        <v>-18.09983719559521</v>
       </c>
       <c r="F68">
-        <v>-0.03884063802997097</v>
+        <v>0.4014407783949803</v>
       </c>
       <c r="G68">
-        <v>-13.77365332280937</v>
+        <v>-11.65231036524579</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.029182215142133</v>
       </c>
       <c r="E69">
-        <v>-19.54737296909506</v>
+        <v>-18.75139856429283</v>
       </c>
       <c r="F69">
-        <v>0.1407055114246135</v>
+        <v>0.6663675844235125</v>
       </c>
       <c r="G69">
-        <v>-12.57679344926943</v>
+        <v>-12.26907162030309</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.926462828719018</v>
       </c>
       <c r="E70">
-        <v>-18.9236526585966</v>
+        <v>-18.66259066052841</v>
       </c>
       <c r="F70">
-        <v>0.4733380987535605</v>
+        <v>0.3715052371926117</v>
       </c>
       <c r="G70">
-        <v>-12.05864010364486</v>
+        <v>-11.99681897624451</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.806578414005803</v>
       </c>
       <c r="E71">
-        <v>-19.1852535450717</v>
+        <v>-19.1533142178956</v>
       </c>
       <c r="F71">
-        <v>0.2391511786755151</v>
+        <v>0.32611401698881</v>
       </c>
       <c r="G71">
-        <v>-12.80138416919912</v>
+        <v>-12.29967761381365</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.674513516737788</v>
       </c>
       <c r="E72">
-        <v>-19.58639030114515</v>
+        <v>-19.32156966965059</v>
       </c>
       <c r="F72">
-        <v>0.04255888480612244</v>
+        <v>0.3858359932610432</v>
       </c>
       <c r="G72">
-        <v>-12.25050608091886</v>
+        <v>-11.7213948295593</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.527681605655451</v>
       </c>
       <c r="E73">
-        <v>-18.83315110555331</v>
+        <v>-18.28257923570074</v>
       </c>
       <c r="F73">
-        <v>0.2025406529413882</v>
+        <v>0.3696463807407296</v>
       </c>
       <c r="G73">
-        <v>-12.56333277110675</v>
+        <v>-11.61484161083232</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.363765878694463</v>
       </c>
       <c r="E74">
-        <v>-18.79479493070834</v>
+        <v>-18.7594094348124</v>
       </c>
       <c r="F74">
-        <v>0.1352995857539439</v>
+        <v>0.1798177067151949</v>
       </c>
       <c r="G74">
-        <v>-12.87238874992541</v>
+        <v>-11.53213094107917</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.183858166472074</v>
       </c>
       <c r="E75">
-        <v>-18.51956333747015</v>
+        <v>-19.20035600588728</v>
       </c>
       <c r="F75">
-        <v>0.3364222209492471</v>
+        <v>0.09022314516320599</v>
       </c>
       <c r="G75">
-        <v>-11.94884255028939</v>
+        <v>-11.87457377166138</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.981663095916146</v>
       </c>
       <c r="E76">
-        <v>-19.85027353852012</v>
+        <v>-18.83032533777252</v>
       </c>
       <c r="F76">
-        <v>-0.2097933040479134</v>
+        <v>-0.06766533854518537</v>
       </c>
       <c r="G76">
-        <v>-11.9445189778151</v>
+        <v>-11.93438539791939</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.759416781292729</v>
       </c>
       <c r="E77">
-        <v>-19.50633140916354</v>
+        <v>-19.83962256765408</v>
       </c>
       <c r="F77">
-        <v>0.1422214237717366</v>
+        <v>0.2684513620799364</v>
       </c>
       <c r="G77">
-        <v>-11.71091364238197</v>
+        <v>-12.01722848949411</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.513440900903193</v>
       </c>
       <c r="E78">
-        <v>-20.87017645452763</v>
+        <v>-19.34871787132658</v>
       </c>
       <c r="F78">
-        <v>-0.1522110007771113</v>
+        <v>0.3186703075072537</v>
       </c>
       <c r="G78">
-        <v>-10.54419794124986</v>
+        <v>-11.58003784557796</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.242578268266327</v>
       </c>
       <c r="E79">
-        <v>-21.10738697999742</v>
+        <v>-20.81674046123712</v>
       </c>
       <c r="F79">
-        <v>-0.3864327122860743</v>
+        <v>0.1811041612917426</v>
       </c>
       <c r="G79">
-        <v>-11.24785108507641</v>
+        <v>-11.16690493609569</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.947307557007791</v>
       </c>
       <c r="E80">
-        <v>-21.21538202813235</v>
+        <v>-21.01247469327066</v>
       </c>
       <c r="F80">
-        <v>-0.2046574261505564</v>
+        <v>-0.09302414984708664</v>
       </c>
       <c r="G80">
-        <v>-11.07808962036813</v>
+        <v>-10.15969131904567</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.623384976304546</v>
       </c>
       <c r="E81">
-        <v>-21.21564467962479</v>
+        <v>-22.04747101314574</v>
       </c>
       <c r="F81">
-        <v>0.02930831983094155</v>
+        <v>-0.01613177404962533</v>
       </c>
       <c r="G81">
-        <v>-10.80586015012832</v>
+        <v>-10.21699024123937</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.273649362074459</v>
       </c>
       <c r="E82">
-        <v>-23.82537707940117</v>
+        <v>-22.64410652060433</v>
       </c>
       <c r="F82">
-        <v>-0.3460290922145284</v>
+        <v>0.02385600558571521</v>
       </c>
       <c r="G82">
-        <v>-10.35461624039796</v>
+        <v>-9.751600370419711</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.895239566694991</v>
       </c>
       <c r="E83">
-        <v>-24.14224346266588</v>
+        <v>-22.29237994442857</v>
       </c>
       <c r="F83">
-        <v>-0.2418163311053366</v>
+        <v>0.02419812132307141</v>
       </c>
       <c r="G83">
-        <v>-10.12510936034244</v>
+        <v>-10.22852749244374</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.490329104813076</v>
       </c>
       <c r="E84">
-        <v>-24.46688523580176</v>
+        <v>-23.33412821904909</v>
       </c>
       <c r="F84">
-        <v>0.1203376137245792</v>
+        <v>-0.3595521900652304</v>
       </c>
       <c r="G84">
-        <v>-9.733213600494597</v>
+        <v>-8.991221028777748</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.061604895341467</v>
       </c>
       <c r="E85">
-        <v>-24.84739026429626</v>
+        <v>-24.21648326554763</v>
       </c>
       <c r="F85">
-        <v>-0.29523277470746</v>
+        <v>-0.07920118299657128</v>
       </c>
       <c r="G85">
-        <v>-9.900065095673865</v>
+        <v>-9.926377311619992</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.6110583216837981</v>
       </c>
       <c r="E86">
-        <v>-26.1691703146031</v>
+        <v>-26.23616003059857</v>
       </c>
       <c r="F86">
-        <v>0.02077447884730105</v>
+        <v>0.1942478668719623</v>
       </c>
       <c r="G86">
-        <v>-10.06322202203131</v>
+        <v>-8.740864332915903</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.1481854206185712</v>
       </c>
       <c r="E87">
-        <v>-27.43110205242457</v>
+        <v>-26.90934939115682</v>
       </c>
       <c r="F87">
-        <v>-0.5061715636259373</v>
+        <v>-0.01190544356054225</v>
       </c>
       <c r="G87">
-        <v>-9.318203611691562</v>
+        <v>-8.690616872720845</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.3209696310816686</v>
       </c>
       <c r="E88">
-        <v>-29.30066896106925</v>
+        <v>-28.41258992342502</v>
       </c>
       <c r="F88">
-        <v>-0.3654344269925097</v>
+        <v>-0.2551795540472983</v>
       </c>
       <c r="G88">
-        <v>-9.359016017099696</v>
+        <v>-8.415921046054278</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.7843935110235593</v>
       </c>
       <c r="E89">
-        <v>-29.70378013181005</v>
+        <v>-30.23422293469851</v>
       </c>
       <c r="F89">
-        <v>-0.3566686431360853</v>
+        <v>-0.2817245874700084</v>
       </c>
       <c r="G89">
-        <v>-8.873484787219105</v>
+        <v>-9.096936679483294</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.2291242859292</v>
       </c>
       <c r="E90">
-        <v>-31.05861124966187</v>
+        <v>-31.55097637885684</v>
       </c>
       <c r="F90">
-        <v>-0.5537157107096149</v>
+        <v>-0.3785416844070063</v>
       </c>
       <c r="G90">
-        <v>-8.733832734190491</v>
+        <v>-8.483879924884437</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.642191746122349</v>
       </c>
       <c r="E91">
-        <v>-32.2520996313314</v>
+        <v>-32.73308017687109</v>
       </c>
       <c r="F91">
-        <v>-0.5967386285088128</v>
+        <v>-0.3842797854061984</v>
       </c>
       <c r="G91">
-        <v>-9.491225963756031</v>
+        <v>-8.922626525204048</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.00618463125867</v>
       </c>
       <c r="E92">
-        <v>-34.23631165219128</v>
+        <v>-35.06067506054759</v>
       </c>
       <c r="F92">
-        <v>-0.6023508176627794</v>
+        <v>-0.3601088529599116</v>
       </c>
       <c r="G92">
-        <v>-9.537848376585588</v>
+        <v>-8.573330865355544</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.30667286027081</v>
       </c>
       <c r="E93">
-        <v>-36.20200674283378</v>
+        <v>-36.17463664593142</v>
       </c>
       <c r="F93">
-        <v>-0.7345872480086786</v>
+        <v>-0.3297251649926285</v>
       </c>
       <c r="G93">
-        <v>-9.956609213484617</v>
+        <v>-8.610551328853571</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.528406367577618</v>
       </c>
       <c r="E94">
-        <v>-38.330482360156</v>
+        <v>-38.01355710672919</v>
       </c>
       <c r="F94">
-        <v>-0.8684017182569107</v>
+        <v>-0.6045476480150037</v>
       </c>
       <c r="G94">
-        <v>-9.062629496059825</v>
+        <v>-8.742367320590732</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.660169625642291</v>
       </c>
       <c r="E95">
-        <v>-39.5965576516945</v>
+        <v>-40.68981505391526</v>
       </c>
       <c r="F95">
-        <v>-1.090392585063539</v>
+        <v>-0.6961145523530583</v>
       </c>
       <c r="G95">
-        <v>-9.738136381711493</v>
+        <v>-8.655256935815888</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.686641469588839</v>
       </c>
       <c r="E96">
-        <v>-43.56994263668964</v>
+        <v>-42.02089885407086</v>
       </c>
       <c r="F96">
-        <v>-1.278576121427114</v>
+        <v>-0.5259214992434831</v>
       </c>
       <c r="G96">
-        <v>-9.8019769418908</v>
+        <v>-9.263185655374414</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.610216230988989</v>
       </c>
       <c r="E97">
-        <v>-43.99466368539503</v>
+        <v>-44.2132621826933</v>
       </c>
       <c r="F97">
-        <v>-1.52261067318964</v>
+        <v>-0.7358662472786009</v>
       </c>
       <c r="G97">
-        <v>-9.276424526985959</v>
+        <v>-9.520007846674455</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.411089377549696</v>
       </c>
       <c r="E98">
-        <v>-45.88988892776718</v>
+        <v>-46.80755475034053</v>
       </c>
       <c r="F98">
-        <v>-1.535447882830824</v>
+        <v>-0.8521574334880123</v>
       </c>
       <c r="G98">
-        <v>-9.706467703082826</v>
+        <v>-9.684111589056128</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.115643843642538</v>
       </c>
       <c r="E99">
-        <v>-49.20983775582553</v>
+        <v>-49.18337901431721</v>
       </c>
       <c r="F99">
-        <v>-1.90542244431057</v>
+        <v>-1.197801187612731</v>
       </c>
       <c r="G99">
-        <v>-10.02966302189972</v>
+        <v>-10.19422030902027</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.685035368280037</v>
       </c>
       <c r="E100">
-        <v>-50.85447309627222</v>
+        <v>-51.62971388283033</v>
       </c>
       <c r="F100">
-        <v>-1.941838303705039</v>
+        <v>-1.575756240651048</v>
       </c>
       <c r="G100">
-        <v>-10.54399268742643</v>
+        <v>-10.04206432548983</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.192623083294272</v>
       </c>
       <c r="E101">
-        <v>-53.49665427655057</v>
+        <v>-53.42965550360708</v>
       </c>
       <c r="F101">
-        <v>-2.458766899176223</v>
+        <v>-1.472238479792805</v>
       </c>
       <c r="G101">
-        <v>-10.75895303038238</v>
+        <v>-11.00092080384771</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.5315421302817385</v>
       </c>
       <c r="E102">
-        <v>-55.45368073582389</v>
+        <v>-56.2418548441479</v>
       </c>
       <c r="F102">
-        <v>-2.414950405405143</v>
+        <v>-1.599208978559107</v>
       </c>
       <c r="G102">
-        <v>-10.99681903792456</v>
+        <v>-11.59587549543783</v>
       </c>
     </row>
   </sheetData>
